--- a/studies/adjoint_studies/super_11/results/superMORE_test_11_15_offsets_final.xlsx
+++ b/studies/adjoint_studies/super_11/results/superMORE_test_11_15_offsets_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +473,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>600292.53490755</v>
+        <v>59865.32711320495</v>
       </c>
       <c r="D2" t="n">
-        <v>87313.39173490922</v>
+        <v>7928.851232604944</v>
       </c>
       <c r="E2" t="n">
-        <v>9989673.958738931</v>
+        <v>974741.4236393819</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -495,20 +495,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3.981071705534969e-10</v>
       </c>
       <c r="C3" t="n">
-        <v>476593.3093093293</v>
+        <v>55283.92119818669</v>
       </c>
       <c r="D3" t="n">
-        <v>70061.1955612865</v>
+        <v>7894.849579056514</v>
       </c>
       <c r="E3" t="n">
-        <v>7763515.344900842</v>
+        <v>912521.6368644179</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -517,20 +517,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.584893192461111e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>761663.646964778</v>
+        <v>59525.40690039885</v>
       </c>
       <c r="D4" t="n">
-        <v>112142.4495940768</v>
+        <v>8808.175586495781</v>
       </c>
       <c r="E4" t="n">
-        <v>11858283.68110837</v>
+        <v>1194745.603893367</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -539,20 +539,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>6.309573444801943e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>1194867.906849167</v>
+        <v>132493.18062175</v>
       </c>
       <c r="D5" t="n">
-        <v>158886.8874947283</v>
+        <v>15189.63391472324</v>
       </c>
       <c r="E5" t="n">
-        <v>15766815.03158894</v>
+        <v>1762944.538529957</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -561,20 +561,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2.511886431509582e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1246262.416270505</v>
+        <v>152018.0760050262</v>
       </c>
       <c r="D6" t="n">
-        <v>63629.52765656311</v>
+        <v>6567.090463823532</v>
       </c>
       <c r="E6" t="n">
-        <v>38965487.582444</v>
+        <v>6576801.939142006</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>13679.76230487605</v>
+        <v>1805.053528448133</v>
       </c>
       <c r="D7" t="n">
-        <v>565.9477640424836</v>
+        <v>66.88109946985008</v>
       </c>
       <c r="E7" t="n">
-        <v>3588928.470177398</v>
+        <v>562844.1921364329</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -605,20 +605,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3.981071705534969e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1088.780853917002</v>
+        <v>162.5970480820144</v>
       </c>
       <c r="D8" t="n">
-        <v>45.3228707570073</v>
+        <v>4.93856347910102</v>
       </c>
       <c r="E8" t="n">
-        <v>253280.8051728884</v>
+        <v>35084.02182274357</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -627,20 +627,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.584893192461114e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>92.04258811725627</v>
+        <v>8.060698959514287</v>
       </c>
       <c r="D9" t="n">
-        <v>3.4395417416147</v>
+        <v>1.322843953397164</v>
       </c>
       <c r="E9" t="n">
-        <v>19583.62601071303</v>
+        <v>1670.791984543126</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -649,20 +649,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>6.30957344480193e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>5.242009970499962</v>
+        <v>1.80718955171</v>
       </c>
       <c r="D10" t="n">
-        <v>1.299562406171304</v>
+        <v>1.276532496587718</v>
       </c>
       <c r="E10" t="n">
-        <v>1026.579226982834</v>
+        <v>116.3878882608105</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -671,20 +671,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2.511886431509577e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>1.763586706341727</v>
+        <v>1.716271785857796</v>
       </c>
       <c r="D11" t="n">
-        <v>1.276340605245794</v>
+        <v>1.276281055146618</v>
       </c>
       <c r="E11" t="n">
-        <v>83.72494520320849</v>
+        <v>12.35409882258493</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -693,20 +693,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.0001</v>
       </c>
       <c r="C12" t="n">
-        <v>1.715946022312514</v>
+        <v>1.715737350432942</v>
       </c>
       <c r="D12" t="n">
-        <v>1.27626862050799</v>
+        <v>1.276275115043095</v>
       </c>
       <c r="E12" t="n">
-        <v>11.31068984940288</v>
+        <v>8.273586563830825</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -715,20 +715,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.0003981071705534969</v>
       </c>
       <c r="C13" t="n">
-        <v>1.715944553920406</v>
+        <v>1.715935899352918</v>
       </c>
       <c r="D13" t="n">
-        <v>1.27628907266147</v>
+        <v>1.276288202595548</v>
       </c>
       <c r="E13" t="n">
-        <v>7.531574657483053</v>
+        <v>7.558845112089345</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -737,20 +737,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.001584893192461111</v>
       </c>
       <c r="C14" t="n">
-        <v>1.71571340673572</v>
+        <v>1.715715598270635</v>
       </c>
       <c r="D14" t="n">
-        <v>1.276001317779174</v>
+        <v>1.276001207530226</v>
       </c>
       <c r="E14" t="n">
-        <v>7.067395429793367</v>
+        <v>7.062132197350196</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -759,20 +759,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.00630957344480193</v>
       </c>
       <c r="C15" t="n">
-        <v>54.01360356504225</v>
+        <v>54.00989078131857</v>
       </c>
       <c r="D15" t="n">
-        <v>9.215216201787777</v>
+        <v>9.214720193389779</v>
       </c>
       <c r="E15" t="n">
-        <v>779.3881878090605</v>
+        <v>779.3370425033737</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -781,20 +781,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10^-7</t>
+          <t>10^-6</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.02511886431509582</v>
       </c>
       <c r="C16" t="n">
-        <v>37447669.99002089</v>
+        <v>3675383.115239332</v>
       </c>
       <c r="D16" t="n">
-        <v>19854585.42928483</v>
+        <v>1971864.526225799</v>
       </c>
       <c r="E16" t="n">
-        <v>351809936.3413869</v>
+        <v>35249557.6971172</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -803,660 +803,330 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1e-10</v>
       </c>
-      <c r="C17" t="n">
-        <v>5999316.622844454</v>
-      </c>
-      <c r="D17" t="n">
-        <v>794820.1557709106</v>
-      </c>
-      <c r="E17" t="n">
-        <v>113388006.2849744</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3.981071705534969e-10</v>
       </c>
-      <c r="C18" t="n">
-        <v>4857063.69046843</v>
-      </c>
-      <c r="D18" t="n">
-        <v>710352.7293193525</v>
-      </c>
-      <c r="E18" t="n">
-        <v>87641107.606934</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1.584893192461111e-09</v>
       </c>
-      <c r="C19" t="n">
-        <v>6921358.562819807</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1008612.188799326</v>
-      </c>
-      <c r="E19" t="n">
-        <v>104130263.9959931</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>6.309573444801943e-09</v>
       </c>
-      <c r="C20" t="n">
-        <v>11115429.98376454</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1629061.677435801</v>
-      </c>
-      <c r="E20" t="n">
-        <v>145130264.0681289</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2.511886431509582e-08</v>
       </c>
-      <c r="C21" t="n">
-        <v>13620055.09357836</v>
-      </c>
-      <c r="D21" t="n">
-        <v>580482.2907980679</v>
-      </c>
-      <c r="E21" t="n">
-        <v>409917820.9297131</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1e-07</v>
       </c>
-      <c r="C22" t="n">
-        <v>284550.1162964262</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4656.485913457223</v>
-      </c>
-      <c r="E22" t="n">
-        <v>47161660.86754937</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3.981071705534969e-07</v>
       </c>
-      <c r="C23" t="n">
-        <v>7614.762869278754</v>
-      </c>
-      <c r="D23" t="n">
-        <v>402.8645678453047</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1645501.132309886</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1.584893192461114e-06</v>
       </c>
-      <c r="C24" t="n">
-        <v>941.1953770620818</v>
-      </c>
-      <c r="D24" t="n">
-        <v>28.51876114335203</v>
-      </c>
-      <c r="E24" t="n">
-        <v>201501.7648208521</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>6.30957344480193e-06</v>
       </c>
-      <c r="C25" t="n">
-        <v>48.04561011560891</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.36447788656795</v>
-      </c>
-      <c r="E25" t="n">
-        <v>10005.92300590273</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2.511886431509577e-05</v>
       </c>
-      <c r="C26" t="n">
-        <v>2.951557091917193</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.282598400771927</v>
-      </c>
-      <c r="E26" t="n">
-        <v>485.4722513518214</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0.0001</v>
       </c>
-      <c r="C27" t="n">
-        <v>1.725446554188337</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.276315413643436</v>
-      </c>
-      <c r="E27" t="n">
-        <v>40.21138849717293</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0.0003981071705534969</v>
       </c>
-      <c r="C28" t="n">
-        <v>1.715939847402832</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.276300988509826</v>
-      </c>
-      <c r="E28" t="n">
-        <v>8.129426942398817</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0.001584893192461111</v>
       </c>
-      <c r="C29" t="n">
-        <v>1.715711965795431</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.275999546809788</v>
-      </c>
-      <c r="E29" t="n">
-        <v>7.063358899893179</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0.00630957344480193</v>
       </c>
-      <c r="C30" t="n">
-        <v>54.01359437876985</v>
-      </c>
-      <c r="D30" t="n">
-        <v>9.21521278044046</v>
-      </c>
-      <c r="E30" t="n">
-        <v>779.3883614284872</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10^-8</t>
+          <t>Adjoint</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0.02511886431509582</v>
       </c>
-      <c r="C31" t="n">
-        <v>370260527.593013</v>
-      </c>
-      <c r="D31" t="n">
-        <v>197598186.5761071</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3541892990.197613</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1e-10</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3.981071705534969e-10</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1.584893192461111e-09</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>6.309573444801943e-09</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2.511886431509582e-08</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3.981071705534969e-07</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1.584893192461114e-06</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>6.30957344480193e-06</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>2.511886431509577e-05</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.0003981071705534969</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.001584893192461111</v>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.00630957344480193</v>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Adjoint</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.02511886431509582</v>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>0</v>
       </c>
     </row>
